--- a/AAII_Financials/Quarterly/LOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
   <si>
     <t>LOT</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,108 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="G7" s="2">
-        <v>44926</v>
-      </c>
       <c r="H7" s="2">
-        <v>44834</v>
-      </c>
-      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="I7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="2">
+        <v>44742</v>
+      </c>
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>173100</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>361100</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>187900</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+        <v>2400</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>142800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>292600</v>
+      </c>
+      <c r="F9" s="3">
+        <v>160300</v>
+      </c>
+      <c r="G9" s="3">
+        <v>123900</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1800</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>4</v>
@@ -768,25 +780,31 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>68500</v>
+      </c>
+      <c r="F10" s="3">
+        <v>27600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>600</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>4</v>
@@ -797,8 +815,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,25 +834,27 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>4</v>
+      <c r="D12" s="3">
+        <v>104700</v>
+      </c>
+      <c r="E12" s="3">
+        <v>134200</v>
+      </c>
+      <c r="F12" s="3">
+        <v>82000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>151300</v>
+      </c>
+      <c r="H12" s="3">
+        <v>126600</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>4</v>
@@ -839,8 +865,14 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,8 +900,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -897,37 +935,49 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>15500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+        <v>2200</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,66 +986,80 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1200</v>
+        <v>406400</v>
       </c>
       <c r="E17" s="3">
-        <v>800</v>
+        <v>589100</v>
       </c>
       <c r="F17" s="3">
-        <v>2700</v>
+        <v>351400</v>
       </c>
       <c r="G17" s="3">
-        <v>1400</v>
+        <v>474400</v>
       </c>
       <c r="H17" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1000</v>
+        <v>186800</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K17" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M17" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-233300</v>
       </c>
       <c r="E18" s="3">
-        <v>-800</v>
+        <v>-228000</v>
       </c>
       <c r="F18" s="3">
-        <v>-2700</v>
+        <v>-163500</v>
       </c>
       <c r="G18" s="3">
-        <v>-1400</v>
+        <v>-344400</v>
       </c>
       <c r="H18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1000</v>
+        <v>-184400</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K18" s="3">
         <v>-500</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1007,37 +1071,45 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-20800</v>
       </c>
       <c r="E20" s="3">
-        <v>3000</v>
+        <v>6900</v>
       </c>
       <c r="F20" s="3">
-        <v>-1000</v>
+        <v>-4800</v>
       </c>
       <c r="G20" s="3">
-        <v>2400</v>
+        <v>-5000</v>
       </c>
       <c r="H20" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I20" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>5000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>5700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1050,11 +1122,11 @@
       <c r="F21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
+      <c r="G21" s="3">
+        <v>-334000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-198400</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>4</v>
@@ -1065,95 +1137,119 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>5500</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1300</v>
+        <v>-258100</v>
       </c>
       <c r="E23" s="3">
-        <v>2200</v>
+        <v>-224000</v>
       </c>
       <c r="F23" s="3">
-        <v>-3700</v>
+        <v>-172200</v>
       </c>
       <c r="G23" s="3">
-        <v>1100</v>
+        <v>-353000</v>
       </c>
       <c r="H23" s="3">
-        <v>600</v>
-      </c>
-      <c r="I23" s="3">
+        <v>-206200</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="3">
         <v>4500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>4700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1181,66 +1277,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1300</v>
+        <v>-258200</v>
       </c>
       <c r="E26" s="3">
-        <v>2200</v>
+        <v>-223700</v>
       </c>
       <c r="F26" s="3">
-        <v>-3700</v>
+        <v>-173600</v>
       </c>
       <c r="G26" s="3">
-        <v>1100</v>
+        <v>-352900</v>
       </c>
       <c r="H26" s="3">
-        <v>600</v>
-      </c>
-      <c r="I26" s="3">
+        <v>-206300</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="3">
         <v>4500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>4700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1300</v>
+        <v>-260800</v>
       </c>
       <c r="E27" s="3">
-        <v>2200</v>
+        <v>-233200</v>
       </c>
       <c r="F27" s="3">
-        <v>-3700</v>
+        <v>-176500</v>
       </c>
       <c r="G27" s="3">
-        <v>1100</v>
+        <v>-347400</v>
       </c>
       <c r="H27" s="3">
-        <v>600</v>
-      </c>
-      <c r="I27" s="3">
+        <v>-206300</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="3">
         <v>4500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>4700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1268,8 +1382,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1297,8 +1417,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1326,8 +1452,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1355,66 +1487,84 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>20800</v>
       </c>
       <c r="E32" s="3">
-        <v>-3000</v>
+        <v>-6900</v>
       </c>
       <c r="F32" s="3">
-        <v>1000</v>
+        <v>4800</v>
       </c>
       <c r="G32" s="3">
-        <v>-2400</v>
+        <v>5000</v>
       </c>
       <c r="H32" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="I32" s="3">
+        <v>16300</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>-5000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-5700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1300</v>
+        <v>-260800</v>
       </c>
       <c r="E33" s="3">
-        <v>2200</v>
+        <v>-233200</v>
       </c>
       <c r="F33" s="3">
-        <v>-3700</v>
+        <v>-176500</v>
       </c>
       <c r="G33" s="3">
-        <v>1100</v>
+        <v>-347400</v>
       </c>
       <c r="H33" s="3">
-        <v>600</v>
-      </c>
-      <c r="I33" s="3">
+        <v>-206300</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" s="3">
         <v>4500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>4700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1442,71 +1592,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1300</v>
+        <v>-260800</v>
       </c>
       <c r="E35" s="3">
-        <v>2200</v>
+        <v>-233200</v>
       </c>
       <c r="F35" s="3">
-        <v>-3700</v>
+        <v>-176500</v>
       </c>
       <c r="G35" s="3">
-        <v>1100</v>
+        <v>-347400</v>
       </c>
       <c r="H35" s="3">
-        <v>600</v>
-      </c>
-      <c r="I35" s="3">
+        <v>-206300</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" s="3">
         <v>4500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>4700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="G38" s="2">
-        <v>44926</v>
-      </c>
       <c r="H38" s="2">
-        <v>44834</v>
-      </c>
-      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="I38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K38" s="2">
+        <v>44742</v>
+      </c>
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1518,8 +1686,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1531,269 +1701,325 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>232900</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>418900</v>
       </c>
       <c r="F41" s="3">
-        <v>0</v>
+        <v>416600</v>
       </c>
       <c r="G41" s="3">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3">
+        <v>548300</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3">
-        <v>100</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+        <v>187600</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>146100</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>99100</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>34300</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>13600</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>368500</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>265200</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>272900</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>125600</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>397700</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>100500</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>192100</v>
       </c>
       <c r="G45" s="3">
-        <v>100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
-      </c>
-      <c r="I45" s="3">
+        <v>219900</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>1332700</v>
       </c>
       <c r="E46" s="3">
-        <v>100</v>
+        <v>883700</v>
       </c>
       <c r="F46" s="3">
-        <v>100</v>
+        <v>916000</v>
       </c>
       <c r="G46" s="3">
-        <v>100</v>
-      </c>
-      <c r="H46" s="3">
-        <v>300</v>
-      </c>
-      <c r="I46" s="3">
+        <v>907400</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="3">
         <v>400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>231000</v>
+        <v>514600</v>
       </c>
       <c r="E47" s="3">
-        <v>227300</v>
+        <v>3300</v>
       </c>
       <c r="F47" s="3">
-        <v>224400</v>
+        <v>3300</v>
       </c>
       <c r="G47" s="3">
-        <v>290700</v>
-      </c>
-      <c r="H47" s="3">
-        <v>288200</v>
-      </c>
-      <c r="I47" s="3">
+        <v>7300</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
         <v>286900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>286600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>286500</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>520800</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
+        <v>527700</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>489200</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+        <v>457200</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>116400</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>116400</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>116400</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>116400</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1821,8 +2047,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1850,37 +2082,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>53600</v>
+      </c>
+      <c r="F52" s="3">
+        <v>54100</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>106900</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1908,37 +2152,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>231000</v>
+        <v>2543500</v>
       </c>
       <c r="E54" s="3">
-        <v>227500</v>
+        <v>1584700</v>
       </c>
       <c r="F54" s="3">
-        <v>224500</v>
+        <v>1578800</v>
       </c>
       <c r="G54" s="3">
-        <v>290700</v>
-      </c>
-      <c r="H54" s="3">
-        <v>288500</v>
-      </c>
-      <c r="I54" s="3">
+        <v>1595200</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
         <v>287400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>287500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>287600</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1950,8 +2206,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1963,138 +2221,164 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>444600</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>360500</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>289300</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+        <v>156300</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>462800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>625700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>648100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>749400</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10800</v>
+        <v>795100</v>
       </c>
       <c r="E59" s="3">
-        <v>8800</v>
+        <v>771100</v>
       </c>
       <c r="F59" s="3">
-        <v>7600</v>
+        <v>591400</v>
       </c>
       <c r="G59" s="3">
-        <v>3900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I59" s="3">
+        <v>550900</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10800</v>
+        <v>1702500</v>
       </c>
       <c r="E60" s="3">
-        <v>8800</v>
+        <v>1757300</v>
       </c>
       <c r="F60" s="3">
-        <v>7600</v>
+        <v>1528800</v>
       </c>
       <c r="G60" s="3">
-        <v>3900</v>
-      </c>
-      <c r="H60" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I60" s="3">
+        <v>1456500</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>1200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>157100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>157300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>150200</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2108,37 +2392,49 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12600</v>
+        <v>664100</v>
       </c>
       <c r="E62" s="3">
-        <v>12200</v>
+        <v>497300</v>
       </c>
       <c r="F62" s="3">
-        <v>12500</v>
+        <v>487400</v>
       </c>
       <c r="G62" s="3">
-        <v>10600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>10600</v>
-      </c>
-      <c r="I62" s="3">
+        <v>398500</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>11600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>16200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2166,8 +2462,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,8 +2497,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2224,37 +2532,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>23400</v>
+        <v>2517900</v>
       </c>
       <c r="E66" s="3">
-        <v>21000</v>
+        <v>2406400</v>
       </c>
       <c r="F66" s="3">
-        <v>20100</v>
+        <v>2161600</v>
       </c>
       <c r="G66" s="3">
-        <v>14500</v>
-      </c>
-      <c r="H66" s="3">
-        <v>13300</v>
-      </c>
-      <c r="I66" s="3">
+        <v>1998700</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>12800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>17300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2266,8 +2586,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2617,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2324,8 +2652,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2333,13 +2667,13 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>383500</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>373500</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>368700</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -2353,8 +2687,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2382,37 +2722,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-23400</v>
+        <v>-1846600</v>
       </c>
       <c r="E72" s="3">
-        <v>-20800</v>
+        <v>-1588800</v>
       </c>
       <c r="F72" s="3">
-        <v>-20100</v>
+        <v>-1365600</v>
       </c>
       <c r="G72" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-13100</v>
-      </c>
-      <c r="I72" s="3">
+        <v>-1193900</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-12300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-16400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-21100</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2440,8 +2792,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2469,8 +2827,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2498,37 +2862,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>207600</v>
+        <v>25600</v>
       </c>
       <c r="E76" s="3">
-        <v>206500</v>
+        <v>-1205300</v>
       </c>
       <c r="F76" s="3">
-        <v>204400</v>
+        <v>-956200</v>
       </c>
       <c r="G76" s="3">
-        <v>276200</v>
-      </c>
-      <c r="H76" s="3">
-        <v>275200</v>
-      </c>
-      <c r="I76" s="3">
+        <v>-772200</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>274600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>270100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2556,71 +2932,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="G80" s="2">
-        <v>44926</v>
-      </c>
       <c r="H80" s="2">
-        <v>44834</v>
-      </c>
-      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="I80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K80" s="2">
+        <v>44742</v>
+      </c>
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1300</v>
+        <v>-260800</v>
       </c>
       <c r="E81" s="3">
-        <v>2200</v>
+        <v>-233200</v>
       </c>
       <c r="F81" s="3">
-        <v>-3700</v>
+        <v>-176500</v>
       </c>
       <c r="G81" s="3">
-        <v>1100</v>
+        <v>-347400</v>
       </c>
       <c r="H81" s="3">
-        <v>600</v>
-      </c>
-      <c r="I81" s="3">
+        <v>-206300</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K81" s="3">
         <v>4500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>4700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2632,8 +3026,10 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2661,8 +3057,14 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2690,8 +3092,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2719,8 +3127,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2748,8 +3162,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2777,8 +3197,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2806,37 +3232,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>1000</v>
+      <c r="D89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E89" s="3">
-        <v>300</v>
-      </c>
-      <c r="F89" s="3">
-        <v>1000</v>
+        <v>26400</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G89" s="3">
+        <v>-303700</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2848,16 +3286,18 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-54900</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-45600</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -2877,8 +3317,14 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2906,8 +3352,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2935,37 +3387,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-1000</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E94" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F94" s="3">
-        <v>69200</v>
+        <v>-52500</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+        <v>-103700</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2977,8 +3441,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3006,8 +3472,14 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,8 +3507,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3064,8 +3542,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3093,91 +3577,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-70200</v>
+        <v>-26200</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+        <v>415300</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
+        <v>9800</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+        <v>-18400</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
+        <v>-42500</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>LOT</t>
   </si>
@@ -656,94 +656,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>225000</v>
+      </c>
+      <c r="E8" s="3">
         <v>173100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>361100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>187900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>130000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
+        <v>9600</v>
+      </c>
+      <c r="J8" s="3">
         <v>2400</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -751,32 +757,35 @@
       <c r="M8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>204400</v>
+      </c>
+      <c r="E9" s="3">
         <v>142800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>292600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>160300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>123900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J9" s="3">
         <v>1800</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
@@ -786,32 +795,35 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E10" s="3">
         <v>30300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>68500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>27600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J10" s="3">
         <v>600</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
@@ -821,8 +833,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,32 +851,33 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>70200</v>
+      </c>
+      <c r="E12" s="3">
         <v>104700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>134200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>82000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>151300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
+        <v>443200</v>
+      </c>
+      <c r="J12" s="3">
         <v>126600</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
@@ -871,8 +887,11 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,8 +925,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -941,8 +963,11 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -955,20 +980,20 @@
       <c r="F15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="3">
         <v>15500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
+        <v>12800</v>
+      </c>
+      <c r="J15" s="3">
         <v>2200</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -976,8 +1001,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,78 +1016,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>429400</v>
+      </c>
+      <c r="E17" s="3">
         <v>406400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>589100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>351400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>474400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>697000</v>
+      </c>
+      <c r="J17" s="3">
         <v>186800</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L17" s="3">
         <v>500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-204400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-233300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-228000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-163500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-344400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-687400</v>
+      </c>
+      <c r="J18" s="3">
         <v>-184400</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,43 +1108,47 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-20800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="J20" s="3">
         <v>-16300</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>5000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1122,18 +1161,18 @@
       <c r="F21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="3">
         <v>-334000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="3">
         <v>-198400</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1143,34 +1182,37 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E22" s="3">
         <v>3900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
+        <v>8500</v>
+      </c>
+      <c r="J22" s="3">
         <v>5500</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1178,69 +1220,75 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-201800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-258100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-224000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-172200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-353000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-724300</v>
+      </c>
+      <c r="J23" s="3">
         <v>-206200</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L23" s="3">
         <v>4500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1400</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>300</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1248,8 +1296,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,78 +1334,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-202000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-258200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-223700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-173600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-352900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-724600</v>
+      </c>
+      <c r="J26" s="3">
         <v>-206300</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="3">
         <v>4500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-201500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-260800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-233200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-176500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-347400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-724800</v>
+      </c>
+      <c r="J27" s="3">
         <v>-206300</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L27" s="3">
         <v>4500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1448,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1486,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1524,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,78 +1562,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E32" s="3">
         <v>20800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>28400</v>
+      </c>
+      <c r="J32" s="3">
         <v>16300</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>-5000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-201500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-260800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-233200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-176500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-347400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>-724800</v>
+      </c>
+      <c r="J33" s="3">
         <v>-206300</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L33" s="3">
         <v>4500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,83 +1676,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-201500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-260800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-233200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-176500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-347400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>-724800</v>
+      </c>
+      <c r="J35" s="3">
         <v>-206300</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L35" s="3">
         <v>4500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K38" s="2">
+      <c r="K38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +1775,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,52 +1791,56 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>268800</v>
+      </c>
+      <c r="E41" s="3">
         <v>232900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>418900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>416600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>548300</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="3">
         <v>187600</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F42" s="3" t="s">
         <v>4</v>
       </c>
@@ -1764,8 +1856,8 @@
       <c r="J42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -1773,34 +1865,37 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>92500</v>
+      </c>
+      <c r="E43" s="3">
         <v>146100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>99100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>34300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13600</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -1808,34 +1903,37 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>385200</v>
+      </c>
+      <c r="E44" s="3">
         <v>368500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>265200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>272900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>125600</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1843,139 +1941,151 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>532800</v>
+      </c>
+      <c r="E45" s="3">
         <v>397700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>192100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>219900</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1279200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1332700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>883700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>916000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>907400</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3">
         <v>400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>536700</v>
+      </c>
+      <c r="E47" s="3">
         <v>514600</v>
-      </c>
-      <c r="E47" s="3">
-        <v>3300</v>
       </c>
       <c r="F47" s="3">
         <v>3300</v>
       </c>
       <c r="G47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H47" s="3">
         <v>7300</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3">
         <v>286900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>286600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>286500</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>504200</v>
+      </c>
+      <c r="E48" s="3">
         <v>520800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>527700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>489200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>457200</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -1983,13 +2093,16 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>116400</v>
+        <v>116500</v>
       </c>
       <c r="E49" s="3">
         <v>116400</v>
@@ -2000,8 +2113,8 @@
       <c r="G49" s="3">
         <v>116400</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
+      <c r="H49" s="3">
+        <v>116400</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>4</v>
@@ -2009,8 +2122,8 @@
       <c r="J49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2018,8 +2131,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2169,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,43 +2207,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E52" s="3">
         <v>59000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>53600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>54100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>106900</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,43 +2283,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2506300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2543500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1584700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1578800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1595200</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
         <v>287400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>287500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>287600</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2339,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,34 +2355,35 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>472100</v>
+      </c>
+      <c r="E57" s="3">
         <v>444600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>360500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>289300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>156300</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -2258,34 +2391,37 @@
       <c r="M57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>629100</v>
+      </c>
+      <c r="E58" s="3">
         <v>462800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>625700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>648100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>749400</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2293,96 +2429,105 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>739300</v>
+      </c>
+      <c r="E59" s="3">
         <v>795100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>771100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>591400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>550900</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1840500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1702500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1757300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1528800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1456500</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
         <v>1200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>153100</v>
+      </c>
+      <c r="E61" s="3">
         <v>157100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>157300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>150200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>150000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2398,43 +2543,49 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>686800</v>
+      </c>
+      <c r="E62" s="3">
         <v>664100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>497300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>487400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>398500</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>11600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +2619,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2657,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,43 +2695,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2674000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2517900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2406400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2161600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1998700</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
         <v>12800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +2751,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +2787,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +2825,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2667,17 +2837,17 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
         <v>383500</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>373500</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>368700</v>
       </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
         <v>0</v>
       </c>
@@ -2693,8 +2863,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,43 +2901,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2048100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1846600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1588800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1365600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1193900</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-12300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-16400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-21100</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +2977,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3015,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,43 +3053,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-167700</v>
+      </c>
+      <c r="E76" s="3">
         <v>25600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1205300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-956200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-772200</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
         <v>274600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>270100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,83 +3129,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K80" s="2">
+      <c r="K80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-201500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-260800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-233200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-176500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-347400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>-724800</v>
+      </c>
+      <c r="J81" s="3">
         <v>-206300</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L81" s="3">
         <v>4500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,8 +3228,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3063,8 +3264,11 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3302,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3340,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3378,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +3416,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,22 +3454,25 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E89" s="3">
-        <v>26400</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>4</v>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-386900</v>
       </c>
       <c r="G89" s="3">
-        <v>-303700</v>
+        <v>-413300</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>4</v>
@@ -3264,17 +3483,20 @@
       <c r="J89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,8 +3510,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3297,7 +3520,7 @@
         <v>-54900</v>
       </c>
       <c r="E91" s="3">
-        <v>-45600</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -3323,8 +3546,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +3584,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,22 +3622,25 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E94" s="3">
-        <v>-52500</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-198000</v>
       </c>
       <c r="G94" s="3">
-        <v>-103700</v>
+        <v>-145500</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>4</v>
@@ -3419,8 +3651,8 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -3428,8 +3660,11 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,8 +3678,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3478,8 +3714,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +3752,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +3790,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,22 +3828,25 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E100" s="3">
-        <v>-26200</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3">
+        <v>284700</v>
       </c>
       <c r="G100" s="3">
-        <v>415300</v>
+        <v>310900</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>4</v>
@@ -3609,8 +3857,8 @@
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -3618,22 +3866,25 @@
       <c r="M100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E101" s="3">
-        <v>9800</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>4</v>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-12200</v>
       </c>
       <c r="G101" s="3">
-        <v>-18400</v>
+        <v>-22000</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>4</v>
@@ -3644,8 +3895,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3653,22 +3904,25 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E102" s="3">
-        <v>-42500</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>4</v>
+      <c r="E102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-312400</v>
       </c>
       <c r="G102" s="3">
-        <v>-10500</v>
+        <v>-269900</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>4</v>
@@ -3679,13 +3933,16 @@
       <c r="J102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K102" s="3">
+      <c r="K102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
   <si>
     <t>LOT</t>
   </si>
@@ -656,103 +656,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
-        <v>44926</v>
-      </c>
       <c r="J7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="L7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>254700</v>
+      </c>
+      <c r="E8" s="3">
         <v>225000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>173100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>361100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>187900</v>
       </c>
-      <c r="H8" s="3">
-        <v>130000</v>
-      </c>
       <c r="I8" s="3">
-        <v>9600</v>
+        <v>110900</v>
       </c>
       <c r="J8" s="3">
+        <v>19100</v>
+      </c>
+      <c r="K8" s="3">
         <v>2400</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -760,35 +764,38 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>246500</v>
+      </c>
+      <c r="E9" s="3">
         <v>204400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>142800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>292600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>160300</v>
       </c>
-      <c r="H9" s="3">
-        <v>123900</v>
-      </c>
       <c r="I9" s="3">
-        <v>7300</v>
+        <v>105000</v>
       </c>
       <c r="J9" s="3">
+        <v>18900</v>
+      </c>
+      <c r="K9" s="3">
         <v>1800</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
@@ -798,35 +805,38 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E10" s="3">
         <v>20600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30300</v>
       </c>
-      <c r="F10" s="3">
-        <v>68500</v>
-      </c>
       <c r="G10" s="3">
+        <v>68400</v>
+      </c>
+      <c r="H10" s="3">
         <v>27600</v>
       </c>
-      <c r="H10" s="3">
-        <v>6100</v>
-      </c>
       <c r="I10" s="3">
-        <v>2400</v>
+        <v>6000</v>
       </c>
       <c r="J10" s="3">
+        <v>200</v>
+      </c>
+      <c r="K10" s="3">
         <v>600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
@@ -836,8 +846,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -852,35 +865,36 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E12" s="3">
         <v>70200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>104700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>134200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>82000</v>
       </c>
-      <c r="H12" s="3">
-        <v>151300</v>
-      </c>
       <c r="I12" s="3">
-        <v>443200</v>
+        <v>87100</v>
       </c>
       <c r="J12" s="3">
+        <v>65500</v>
+      </c>
+      <c r="K12" s="3">
         <v>126600</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
@@ -890,8 +904,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -928,31 +945,34 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+        <v>1400</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-2200</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -966,37 +986,40 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>4</v>
+      <c r="D15" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E15" s="3">
+        <v>19600</v>
+      </c>
+      <c r="F15" s="3">
+        <v>13700</v>
+      </c>
+      <c r="G15" s="3">
+        <v>3200</v>
       </c>
       <c r="H15" s="3">
-        <v>15500</v>
+        <v>3200</v>
       </c>
       <c r="I15" s="3">
-        <v>12800</v>
+        <v>11300</v>
       </c>
       <c r="J15" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K15" s="3">
         <v>2200</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1004,8 +1027,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1017,84 +1043,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>414700</v>
+      </c>
+      <c r="E17" s="3">
         <v>429400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>406400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>589100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>351400</v>
       </c>
-      <c r="H17" s="3">
-        <v>474400</v>
-      </c>
       <c r="I17" s="3">
-        <v>697000</v>
+        <v>293600</v>
       </c>
       <c r="J17" s="3">
+        <v>180900</v>
+      </c>
+      <c r="K17" s="3">
         <v>186800</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-204400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-233300</v>
       </c>
-      <c r="F18" s="3">
-        <v>-228000</v>
-      </c>
       <c r="G18" s="3">
+        <v>-228100</v>
+      </c>
+      <c r="H18" s="3">
         <v>-163500</v>
       </c>
-      <c r="H18" s="3">
-        <v>-344400</v>
-      </c>
       <c r="I18" s="3">
-        <v>-687400</v>
+        <v>-182600</v>
       </c>
       <c r="J18" s="3">
+        <v>-161800</v>
+      </c>
+      <c r="K18" s="3">
         <v>-184400</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1109,73 +1142,77 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>10400</v>
+        <v>50500</v>
       </c>
       <c r="E20" s="3">
-        <v>-20800</v>
+        <v>1500</v>
       </c>
       <c r="F20" s="3">
-        <v>6900</v>
+        <v>21100</v>
       </c>
       <c r="G20" s="3">
         <v>-4800</v>
       </c>
       <c r="H20" s="3">
-        <v>-5000</v>
+        <v>2200</v>
       </c>
       <c r="I20" s="3">
-        <v>-28400</v>
+        <v>15600</v>
       </c>
       <c r="J20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="K20" s="3">
         <v>-16300</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>5000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-196800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-186300</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-240700</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-220000</v>
       </c>
       <c r="H21" s="3">
-        <v>-334000</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
+        <v>-162500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-187000</v>
       </c>
       <c r="J21" s="3">
+        <v>-156600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-198400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1185,37 +1222,40 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E22" s="3">
         <v>7800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3900</v>
       </c>
-      <c r="H22" s="3">
-        <v>3500</v>
-      </c>
       <c r="I22" s="3">
-        <v>8500</v>
+        <v>3000</v>
       </c>
       <c r="J22" s="3">
+        <v>400</v>
+      </c>
+      <c r="K22" s="3">
         <v>5500</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1223,75 +1263,81 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-205500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-201800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-258100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-224000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-172200</v>
       </c>
-      <c r="H23" s="3">
-        <v>-353000</v>
-      </c>
       <c r="I23" s="3">
-        <v>-724300</v>
+        <v>-193300</v>
       </c>
       <c r="J23" s="3">
+        <v>-159700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-206200</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3">
         <v>4500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1400</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1299,8 +1345,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1337,84 +1386,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-206300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-202000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-258200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-223700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-173600</v>
       </c>
-      <c r="H26" s="3">
-        <v>-352900</v>
-      </c>
       <c r="I26" s="3">
-        <v>-724600</v>
+        <v>-193400</v>
       </c>
       <c r="J26" s="3">
+        <v>-159600</v>
+      </c>
+      <c r="K26" s="3">
         <v>-206300</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3">
         <v>4500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-205800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-201500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-260800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-233200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-176500</v>
       </c>
-      <c r="H27" s="3">
-        <v>-347400</v>
-      </c>
       <c r="I27" s="3">
-        <v>-724800</v>
+        <v>-182500</v>
       </c>
       <c r="J27" s="3">
+        <v>-164900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-206300</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3">
         <v>4500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1451,8 +1509,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1489,8 +1550,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1527,8 +1591,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1565,84 +1632,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-10400</v>
+        <v>-50500</v>
       </c>
       <c r="E32" s="3">
-        <v>20800</v>
+        <v>-1500</v>
       </c>
       <c r="F32" s="3">
-        <v>-6900</v>
+        <v>-21100</v>
       </c>
       <c r="G32" s="3">
         <v>4800</v>
       </c>
       <c r="H32" s="3">
-        <v>5000</v>
+        <v>-2200</v>
       </c>
       <c r="I32" s="3">
-        <v>28400</v>
+        <v>-15600</v>
       </c>
       <c r="J32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K32" s="3">
         <v>16300</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-5000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-205800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-201500</v>
       </c>
-      <c r="E33" s="3">
-        <v>-260800</v>
-      </c>
       <c r="F33" s="3">
-        <v>-233200</v>
+        <v>-257900</v>
       </c>
       <c r="G33" s="3">
-        <v>-176500</v>
+        <v>-223100</v>
       </c>
       <c r="H33" s="3">
-        <v>-347400</v>
+        <v>-171700</v>
       </c>
       <c r="I33" s="3">
-        <v>-724800</v>
+        <v>-189500</v>
       </c>
       <c r="J33" s="3">
+        <v>-157700</v>
+      </c>
+      <c r="K33" s="3">
         <v>-206300</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3">
         <v>4500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1679,89 +1755,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-205800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-201500</v>
       </c>
-      <c r="E35" s="3">
-        <v>-260800</v>
-      </c>
       <c r="F35" s="3">
-        <v>-233200</v>
+        <v>-257900</v>
       </c>
       <c r="G35" s="3">
-        <v>-176500</v>
+        <v>-223100</v>
       </c>
       <c r="H35" s="3">
-        <v>-347400</v>
+        <v>-171700</v>
       </c>
       <c r="I35" s="3">
-        <v>-724800</v>
+        <v>-189500</v>
       </c>
       <c r="J35" s="3">
+        <v>-157700</v>
+      </c>
+      <c r="K35" s="3">
         <v>-206300</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3">
         <v>4500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
-        <v>44926</v>
-      </c>
       <c r="J38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L38" s="2">
+      <c r="L38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1776,8 +1861,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1792,75 +1878,79 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>191300</v>
+      </c>
+      <c r="E41" s="3">
         <v>268800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>232900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>418900</v>
       </c>
-      <c r="G41" s="3">
-        <v>416600</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3">
         <v>548300</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>4</v>
+      <c r="D42" s="3">
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>187600</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
+        <v>5000</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -1868,28 +1958,31 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>151100</v>
+      </c>
+      <c r="E43" s="3">
         <v>92500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>146100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>99100</v>
       </c>
-      <c r="G43" s="3">
-        <v>34300</v>
-      </c>
-      <c r="H43" s="3">
-        <v>13600</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3">
+        <v>28500</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
@@ -1897,8 +1990,8 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -1906,28 +1999,31 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>320800</v>
+      </c>
+      <c r="E44" s="3">
         <v>385200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>368500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>265200</v>
       </c>
-      <c r="G44" s="3">
-        <v>272900</v>
-      </c>
-      <c r="H44" s="3">
-        <v>125600</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3">
+        <v>134500</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
@@ -1935,8 +2031,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -1944,28 +2040,31 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>532800</v>
+        <v>165600</v>
       </c>
       <c r="E45" s="3">
-        <v>397700</v>
+        <v>153900</v>
       </c>
       <c r="F45" s="3">
-        <v>100500</v>
+        <v>309600</v>
       </c>
       <c r="G45" s="3">
-        <v>192100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>219900</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
+        <v>92600</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
+        <v>13400</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
@@ -1973,75 +2072,81 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1294000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1279200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1332700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>883700</v>
       </c>
-      <c r="G46" s="3">
-        <v>916000</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3">
         <v>907400</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="3">
         <v>400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>536700</v>
+        <v>2000</v>
       </c>
       <c r="E47" s="3">
-        <v>514600</v>
+        <v>6800</v>
       </c>
       <c r="F47" s="3">
-        <v>3300</v>
+        <v>2100</v>
       </c>
       <c r="G47" s="3">
         <v>3300</v>
       </c>
-      <c r="H47" s="3">
-        <v>7300</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3">
+        <v>11800</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>4</v>
@@ -2049,46 +2154,49 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
         <v>286900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>286600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>286500</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>496800</v>
+      </c>
+      <c r="E48" s="3">
         <v>504200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>520800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>527700</v>
       </c>
-      <c r="G48" s="3">
-        <v>489200</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3">
         <v>457200</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -2096,8 +2204,11 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2105,7 +2216,7 @@
         <v>116500</v>
       </c>
       <c r="E49" s="3">
-        <v>116400</v>
+        <v>116500</v>
       </c>
       <c r="F49" s="3">
         <v>116400</v>
@@ -2114,19 +2225,19 @@
         <v>116400</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>116400</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2134,8 +2245,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2172,8 +2286,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2210,28 +2327,31 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>69600</v>
+        <v>397100</v>
       </c>
       <c r="E52" s="3">
-        <v>59000</v>
+        <v>375500</v>
       </c>
       <c r="F52" s="3">
+        <v>368600</v>
+      </c>
+      <c r="G52" s="3">
         <v>53600</v>
       </c>
-      <c r="G52" s="3">
-        <v>54100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>106900</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3">
+        <v>102400</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>4</v>
@@ -2239,17 +2359,20 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2286,46 +2409,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2587200</v>
+      </c>
+      <c r="E54" s="3">
         <v>2506300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2543500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1584700</v>
       </c>
-      <c r="G54" s="3">
-        <v>1578800</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="3">
         <v>1595200</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" s="3">
         <v>287400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>287500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>287600</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2340,8 +2469,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2356,28 +2486,29 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>472100</v>
+        <v>549000</v>
       </c>
       <c r="E57" s="3">
+        <v>695100</v>
+      </c>
+      <c r="F57" s="3">
         <v>444600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>360500</v>
       </c>
-      <c r="G57" s="3">
-        <v>289300</v>
-      </c>
-      <c r="H57" s="3">
-        <v>156300</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3">
+        <v>167600</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>4</v>
@@ -2385,8 +2516,8 @@
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -2394,37 +2525,40 @@
       <c r="N57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>629100</v>
+        <v>934700</v>
       </c>
       <c r="E58" s="3">
-        <v>462800</v>
+        <v>644700</v>
       </c>
       <c r="F58" s="3">
-        <v>625700</v>
+        <v>479000</v>
       </c>
       <c r="G58" s="3">
-        <v>648100</v>
+        <v>642400</v>
       </c>
       <c r="H58" s="3">
-        <v>749400</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>766400</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2432,28 +2566,31 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>739300</v>
+        <v>48400</v>
       </c>
       <c r="E59" s="3">
-        <v>795100</v>
+        <v>196100</v>
       </c>
       <c r="F59" s="3">
-        <v>771100</v>
+        <v>62300</v>
       </c>
       <c r="G59" s="3">
-        <v>591400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>550900</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
+        <v>44200</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
+        <v>165200</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
@@ -2461,75 +2598,81 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2130000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1840500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1702500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1757300</v>
       </c>
-      <c r="G60" s="3">
-        <v>1528800</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3">
         <v>1456500</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="3">
         <v>1200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>153100</v>
+        <v>269400</v>
       </c>
       <c r="E61" s="3">
-        <v>157100</v>
+        <v>245800</v>
       </c>
       <c r="F61" s="3">
-        <v>157300</v>
+        <v>257100</v>
       </c>
       <c r="G61" s="3">
-        <v>150200</v>
+        <v>261300</v>
       </c>
       <c r="H61" s="3">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>242300</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2546,28 +2689,31 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>686800</v>
+        <v>256300</v>
       </c>
       <c r="E62" s="3">
-        <v>664100</v>
+        <v>290600</v>
       </c>
       <c r="F62" s="3">
-        <v>497300</v>
+        <v>287300</v>
       </c>
       <c r="G62" s="3">
-        <v>487400</v>
-      </c>
-      <c r="H62" s="3">
-        <v>398500</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
+        <v>116900</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3">
+        <v>39200</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
@@ -2575,17 +2721,20 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>11600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2622,8 +2771,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2660,8 +2812,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2698,28 +2853,31 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2674000</v>
+        <v>2964800</v>
       </c>
       <c r="E66" s="3">
-        <v>2517900</v>
+        <v>2680300</v>
       </c>
       <c r="F66" s="3">
-        <v>2406400</v>
+        <v>2523700</v>
       </c>
       <c r="G66" s="3">
-        <v>2161600</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1998700</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
+        <v>2411900</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3">
+        <v>2005000</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>4</v>
@@ -2727,17 +2885,20 @@
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3">
         <v>12800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2752,8 +2913,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2790,8 +2952,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2828,8 +2993,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2840,19 +3008,19 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
         <v>383500</v>
       </c>
-      <c r="G70" s="3">
-        <v>373500</v>
-      </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>368700</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>368400</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -2866,8 +3034,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2904,46 +3075,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2253900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2048100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1846600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1588800</v>
       </c>
-      <c r="G72" s="3">
-        <v>-1365600</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3">
         <v>-1193900</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-12300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-16400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-21100</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2980,8 +3157,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3018,8 +3198,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3056,46 +3239,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-371000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-167700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1205300</v>
       </c>
-      <c r="G76" s="3">
-        <v>-956200</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3">
         <v>-772200</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
+      <c r="J76" s="3">
+        <v>-452400</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3">
         <v>274600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>270100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3132,89 +3321,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
-        <v>44926</v>
-      </c>
       <c r="J80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L80" s="2">
+      <c r="L80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-205800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-201500</v>
       </c>
-      <c r="E81" s="3">
-        <v>-260800</v>
-      </c>
       <c r="F81" s="3">
-        <v>-233200</v>
+        <v>-257900</v>
       </c>
       <c r="G81" s="3">
-        <v>-176500</v>
+        <v>-223100</v>
       </c>
       <c r="H81" s="3">
-        <v>-347400</v>
+        <v>-171700</v>
       </c>
       <c r="I81" s="3">
-        <v>-724800</v>
+        <v>-189500</v>
       </c>
       <c r="J81" s="3">
+        <v>-157700</v>
+      </c>
+      <c r="K81" s="3">
         <v>-206300</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3">
         <v>4500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3229,31 +3427,32 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3267,8 +3466,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3305,8 +3507,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3343,8 +3548,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3381,8 +3589,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3419,8 +3630,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3457,8 +3671,11 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3468,11 +3685,11 @@
       <c r="E89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F89" s="3">
-        <v>-386900</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-413300</v>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>4</v>
@@ -3486,17 +3703,20 @@
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3511,31 +3731,32 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-54900</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3549,8 +3770,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3587,8 +3811,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3625,8 +3852,11 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3636,11 +3866,11 @@
       <c r="E94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="3">
-        <v>-198000</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-145500</v>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>4</v>
@@ -3654,8 +3884,8 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -3663,8 +3893,11 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3679,31 +3912,32 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3717,8 +3951,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3755,8 +3992,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3793,8 +4033,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3831,8 +4074,11 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3842,11 +4088,11 @@
       <c r="E100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F100" s="3">
-        <v>284700</v>
-      </c>
-      <c r="G100" s="3">
-        <v>310900</v>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>4</v>
@@ -3860,8 +4106,8 @@
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -3869,8 +4115,11 @@
       <c r="N100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3880,26 +4129,26 @@
       <c r="E101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F101" s="3">
-        <v>-12200</v>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G101" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>4</v>
+        <v>16400</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="J101" s="3">
+        <v>4200</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -3907,42 +4156,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>4</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>-312400</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-269900</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
   <si>
     <t>LOT</t>
   </si>
@@ -656,110 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="M7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>271500</v>
+      </c>
+      <c r="E8" s="3">
         <v>254700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>225000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>173100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>361100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>187900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>110900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2400</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -767,38 +770,41 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E9" s="3">
         <v>246500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>204400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>142800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>292600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>160300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>105000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1800</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
@@ -808,38 +814,41 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="E10" s="3">
         <v>8200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>30300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>68400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>27600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>600</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
@@ -849,8 +858,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -866,38 +878,39 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E12" s="3">
         <v>52700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>70200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>104700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>134200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>82000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>87100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>65500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>126600</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
@@ -907,8 +920,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -948,35 +964,38 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I14" s="3">
         <v>4100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -989,40 +1008,43 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E15" s="3">
         <v>13700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>13700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>13700</v>
+      </c>
+      <c r="I15" s="3">
         <v>3200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
+        <v>11300</v>
+      </c>
+      <c r="K15" s="3">
         <v>3200</v>
       </c>
-      <c r="I15" s="3">
-        <v>11300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2200</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1030,8 +1052,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,90 +1069,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>460100</v>
+      </c>
+      <c r="E17" s="3">
         <v>414700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>429400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>406400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>589100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>351400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>293600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>180900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>186800</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="3">
         <v>500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-188600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-160000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-204400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-233300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-228100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-163500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-182600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-161800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-184400</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1143,79 +1175,83 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>224100</v>
+      </c>
+      <c r="E20" s="3">
         <v>50500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>21100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>15600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-16300</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>5000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-393600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-196800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-186300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-240700</v>
       </c>
-      <c r="G21" s="3">
-        <v>-220000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-209500</v>
+      </c>
+      <c r="I21" s="3">
         <v>-162500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-187000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-156600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-198400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1225,40 +1261,43 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E22" s="3">
         <v>8800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5500</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1266,81 +1305,87 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-439900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-205500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-201800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-258100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-224000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-172200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-193300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-159700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-206200</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N23" s="3">
         <v>4500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1348,8 +1393,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1389,90 +1437,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-440800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-206300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-202000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-258200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-223700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-173600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-193400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-159600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-206300</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3">
         <v>4500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-439800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-205800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-201500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-260800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-233200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-176500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-182500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-164900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-206300</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N27" s="3">
         <v>4500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1512,8 +1569,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1553,8 +1613,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1594,8 +1657,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1635,90 +1701,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-224100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-50500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-21100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-15600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>16300</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>-5000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-439800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-205800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-201500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-257900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-223100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-171700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-189500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-157700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-206300</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="3">
         <v>4500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1758,95 +1833,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-439800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-205800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-201500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-257900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-223100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-171700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-189500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-157700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-206300</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3">
         <v>4500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M38" s="2">
+      <c r="M38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1862,8 +1946,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1879,81 +1964,85 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>103100</v>
+      </c>
+      <c r="E41" s="3">
         <v>191300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>268800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>232900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>418900</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3">
         <v>548300</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
         <v>100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>5000</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>2600</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -1961,40 +2050,43 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>270700</v>
+      </c>
+      <c r="E43" s="3">
         <v>151100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>92500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>146100</v>
       </c>
-      <c r="G43" s="3">
-        <v>99100</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="H43" s="3">
+        <v>106500</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>28500</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2002,40 +2094,43 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>221800</v>
+      </c>
+      <c r="E44" s="3">
         <v>320800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>385200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>368500</v>
       </c>
-      <c r="G44" s="3">
-        <v>265200</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="H44" s="3">
+        <v>286600</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>134500</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2043,163 +2138,175 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E45" s="3">
         <v>165600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>153900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>309600</v>
       </c>
-      <c r="G45" s="3">
-        <v>92600</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="H45" s="3">
+        <v>59800</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>13400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1042900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1294000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1279200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1332700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>883700</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3">
         <v>907400</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N46" s="3">
         <v>400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E47" s="3">
         <v>2000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2100</v>
       </c>
-      <c r="G47" s="3">
-        <v>3300</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="H47" s="3">
+        <v>7800</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
         <v>11800</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>286900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>286600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>286500</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>460500</v>
+      </c>
+      <c r="E48" s="3">
         <v>496800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>504200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>520800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>527700</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3">
         <v>457200</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -2207,8 +2314,11 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2219,28 +2329,28 @@
         <v>116500</v>
       </c>
       <c r="F49" s="3">
-        <v>116400</v>
+        <v>116500</v>
       </c>
       <c r="G49" s="3">
         <v>116400</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>116400</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>116400</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2248,8 +2358,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2289,8 +2402,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2330,49 +2446,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>386500</v>
+      </c>
+      <c r="E52" s="3">
         <v>397100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>375500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>368600</v>
       </c>
-      <c r="G52" s="3">
-        <v>53600</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="H52" s="3">
+        <v>49100</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>102400</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2412,49 +2534,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2285700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2587200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2506300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2543500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1584700</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3">
         <v>1595200</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>287400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>287500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>287600</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2470,8 +2598,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2487,40 +2616,41 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>681800</v>
+      </c>
+      <c r="E57" s="3">
         <v>549000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>695100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>444600</v>
       </c>
-      <c r="G57" s="3">
-        <v>360500</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="H57" s="3">
+        <v>605500</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3">
         <v>167600</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -2528,40 +2658,43 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>931600</v>
+      </c>
+      <c r="E58" s="3">
         <v>934700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>644700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>479000</v>
       </c>
-      <c r="G58" s="3">
-        <v>642400</v>
-      </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>643300</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>766400</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2569,114 +2702,123 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>579600</v>
+      </c>
+      <c r="E59" s="3">
         <v>48400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>196100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>62300</v>
       </c>
-      <c r="G59" s="3">
-        <v>44200</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="H59" s="3">
+        <v>235500</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>165200</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2467400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2130000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1840500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1702500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1757300</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3">
         <v>1456500</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>1200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>256300</v>
+      </c>
+      <c r="E61" s="3">
         <v>269400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>245800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>257100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>261300</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>242300</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2692,49 +2834,55 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>119600</v>
+      </c>
+      <c r="E62" s="3">
         <v>256300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>290600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>287300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>116900</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
         <v>39200</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>11600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2774,8 +2922,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2815,8 +2966,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2856,49 +3010,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3145900</v>
+      </c>
+      <c r="E66" s="3">
         <v>2964800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2680300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2523700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2411900</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3">
         <v>2005000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>12800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2914,8 +3074,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2955,8 +3116,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2996,8 +3160,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3011,20 +3178,20 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
         <v>383500</v>
       </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>368700</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>368400</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -3037,8 +3204,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3078,49 +3248,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2693700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2253900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2048100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1846600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1588800</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>-1193900</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-12300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-16400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-21100</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3160,8 +3336,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3201,8 +3380,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3242,49 +3424,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-852900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-371000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-167700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1205300</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3">
         <v>-772200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-452400</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N76" s="3">
         <v>274600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>270100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3324,95 +3512,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M80" s="2">
+      <c r="M80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-439800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-205800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-201500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-257900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-223100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-171700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-189500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-157700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-206300</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N81" s="3">
         <v>4500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3428,8 +3625,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3442,11 +3640,11 @@
       <c r="F83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3">
         <v>7300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1100</v>
       </c>
       <c r="I83" s="3">
         <v>1100</v>
@@ -3455,7 +3653,7 @@
         <v>1100</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -3469,8 +3667,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3510,8 +3711,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3551,8 +3755,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3592,8 +3799,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3633,8 +3843,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3674,8 +3887,11 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3706,17 +3922,20 @@
       <c r="L89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3732,8 +3951,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3758,8 +3978,8 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -3773,8 +3993,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3814,8 +4037,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3855,8 +4081,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3887,8 +4116,8 @@
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -3896,8 +4125,11 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3913,8 +4145,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3939,8 +4172,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -3954,8 +4187,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3995,8 +4231,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4036,8 +4275,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4077,8 +4319,11 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4109,8 +4354,8 @@
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -4118,8 +4363,11 @@
       <c r="O100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4132,26 +4380,26 @@
       <c r="F101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3">
         <v>16400</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-13500</v>
       </c>
       <c r="I101" s="3">
         <v>-13500</v>
       </c>
       <c r="J101" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="K101" s="3">
         <v>4200</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4159,8 +4407,11 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4185,19 +4436,22 @@
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>4</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
   <si>
     <t>LOT</t>
   </si>
@@ -656,116 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="2">
+      <c r="N7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E8" s="3">
         <v>271500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>254700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>225000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>173100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>361100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>187900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>110900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2400</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -773,41 +777,44 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>81700</v>
+      </c>
+      <c r="E9" s="3">
         <v>301000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>246500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>204400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>142800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>292600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>160300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>105000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
@@ -817,41 +824,44 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-29500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>30300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>68400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>27600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>600</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
@@ -861,8 +871,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -879,41 +892,42 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E12" s="3">
         <v>47300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>52700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>70200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>104700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>134200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>82000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>87100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>65500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>126600</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
@@ -923,8 +937,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -967,8 +984,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -978,27 +998,27 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>-1400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1011,8 +1031,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1020,34 +1043,34 @@
         <v>19100</v>
       </c>
       <c r="E15" s="3">
+        <v>19100</v>
+      </c>
+      <c r="F15" s="3">
         <v>13700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>19600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>13700</v>
       </c>
       <c r="H15" s="3">
         <v>13700</v>
       </c>
       <c r="I15" s="3">
+        <v>13700</v>
+      </c>
+      <c r="J15" s="3">
         <v>3200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2200</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1055,8 +1078,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,96 +1096,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>195800</v>
+      </c>
+      <c r="E17" s="3">
         <v>460100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>414700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>429400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>406400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>589100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>351400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>293600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>180900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>186800</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3">
         <v>500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-103000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-188600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-160000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-204400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-233300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-228100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-163500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-182600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-161800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-184400</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1176,85 +1209,89 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E20" s="3">
         <v>224100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>50500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>21100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>15600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-16300</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>5000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-140100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-393600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-196800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-186300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-240700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-209500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-162500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-187000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-156600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-198400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1264,43 +1301,46 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E22" s="3">
         <v>37700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5500</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1308,87 +1348,93 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-182200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-439900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-205500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-201800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-258100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-224000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-172200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-193300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-159700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-206200</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3">
         <v>4500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1396,8 +1442,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1440,96 +1489,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-182800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-440800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-206300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-202000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-258200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-223700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-173600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-193400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-159600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-206300</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3">
         <v>4500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-182800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-439800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-205800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-201500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-260800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-233200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-176500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-182500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-164900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-206300</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3">
         <v>4500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1572,8 +1630,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1616,8 +1677,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1660,8 +1724,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1704,96 +1771,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-56200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-224100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-50500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-21100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-15600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>16300</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
         <v>-5000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-182800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-439800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-205800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-201500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-257900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-223100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-171700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-189500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-157700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-206300</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3">
         <v>4500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1836,101 +1912,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-182800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-439800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-205800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-201500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-257900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-223100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-171700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-189500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-157700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-206300</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3">
         <v>4500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="N38" s="2">
+      <c r="N38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1947,8 +2032,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1965,87 +2051,91 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>122600</v>
+      </c>
+      <c r="E41" s="3">
         <v>103100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>191300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>268800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>232900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>418900</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="3">
         <v>548300</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O41" s="3">
         <v>100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>3400</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>5000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>4000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>2600</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2053,43 +2143,46 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>182300</v>
+      </c>
+      <c r="E43" s="3">
         <v>270700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>151100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>92500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>146100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>106500</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K43" s="3">
         <v>28500</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2097,43 +2190,46 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>143400</v>
+      </c>
+      <c r="E44" s="3">
         <v>221800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>320800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>385200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>368500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>286600</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="3">
         <v>134500</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2141,175 +2237,187 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E45" s="3">
         <v>64600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>165600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>153900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>309600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>59800</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>13400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1013700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1042900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1294000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1279200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1332700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>883700</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="3">
         <v>907400</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O46" s="3">
         <v>400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E47" s="3">
         <v>9700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7800</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
         <v>11800</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O47" s="3">
         <v>286900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>286600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>286500</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>451900</v>
+      </c>
+      <c r="E48" s="3">
         <v>460500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>496800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>504200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>520800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>527700</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="3">
         <v>457200</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -2317,8 +2425,11 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2332,28 +2443,28 @@
         <v>116500</v>
       </c>
       <c r="G49" s="3">
-        <v>116400</v>
+        <v>116500</v>
       </c>
       <c r="H49" s="3">
         <v>116400</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>116400</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>116400</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2361,8 +2472,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2405,8 +2519,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2449,52 +2566,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>394100</v>
+      </c>
+      <c r="E52" s="3">
         <v>386500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>397100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>375500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>368600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>49100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
         <v>102400</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="N52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2537,52 +2660,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2266900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2285700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2587200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2506300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2543500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1584700</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
         <v>1595200</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3">
         <v>287400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>287500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>287600</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2599,8 +2728,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2617,43 +2747,44 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>364500</v>
+      </c>
+      <c r="E57" s="3">
         <v>681800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>549000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>695100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>444600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>605500</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
         <v>167600</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
+      <c r="N57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
@@ -2661,43 +2792,46 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1120100</v>
+      </c>
+      <c r="E58" s="3">
         <v>931600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>934700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>644700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>479000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>643300</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>766400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2705,123 +2839,132 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E59" s="3">
         <v>579600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>196100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>62300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>235500</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>165200</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2246400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2467400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2130000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1840500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1702500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1757300</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>1456500</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>1200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>261000</v>
+      </c>
+      <c r="E61" s="3">
         <v>256300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>269400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>245800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>257100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>261300</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>242300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2837,52 +2980,58 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>498400</v>
+      </c>
+      <c r="E62" s="3">
         <v>119600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>256300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>290600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>287300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>116900</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>39200</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
         <v>11600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2925,8 +3074,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2969,8 +3121,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3013,52 +3168,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3308100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3145900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2964800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2680300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2523700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2411900</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>2005000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>12800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3075,8 +3236,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3119,8 +3281,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3163,8 +3328,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3181,20 +3349,20 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>383500</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>368700</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>368400</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3207,8 +3375,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3251,52 +3422,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2876500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2693700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2253900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2048100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1846600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1588800</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1193900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>-12300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-16400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-21100</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3339,8 +3516,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3383,8 +3563,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3427,52 +3610,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1033500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-852900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-371000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-167700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1205300</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>-772200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-452400</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O76" s="3">
         <v>274600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>270100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3515,101 +3704,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="N80" s="2">
+      <c r="N80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-182800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-439800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-205800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-201500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-257900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-223100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-171700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-189500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-157700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-206300</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3">
         <v>4500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3626,8 +3824,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3643,11 +3842,11 @@
       <c r="G83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3">
         <v>7300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1100</v>
       </c>
       <c r="J83" s="3">
         <v>1100</v>
@@ -3656,7 +3855,7 @@
         <v>1100</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3670,8 +3869,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3714,8 +3916,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3758,8 +3963,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3802,8 +4010,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3846,8 +4057,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3890,8 +4104,11 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3925,17 +4142,20 @@
       <c r="M89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3952,8 +4172,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3981,8 +4202,8 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -3996,8 +4217,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4040,8 +4264,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4084,8 +4311,11 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4119,8 +4349,8 @@
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -4128,8 +4358,11 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4146,8 +4379,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4175,8 +4409,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4190,8 +4424,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4234,8 +4471,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4278,8 +4518,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4322,8 +4565,11 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4357,8 +4603,8 @@
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -4366,8 +4612,11 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4383,26 +4632,26 @@
       <c r="G101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3">
         <v>16400</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-13500</v>
       </c>
       <c r="J101" s="3">
         <v>-13500</v>
       </c>
       <c r="K101" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="L101" s="3">
         <v>4200</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -4410,8 +4659,11 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4439,19 +4691,22 @@
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>4</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>LOT</t>
   </si>
@@ -656,137 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>163300</v>
+      </c>
+      <c r="E8" s="3">
         <v>137400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>125500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>92800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>271500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>254700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>225000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>173100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>361100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>187900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>110900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2400</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -794,50 +797,53 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>146900</v>
+      </c>
+      <c r="E9" s="3">
         <v>126600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>118800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>81700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>301000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>246500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>204400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>142800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>292600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>160300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>105000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1800</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
@@ -847,50 +853,53 @@
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E10" s="3">
         <v>10900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>11100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-29500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>20600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>30300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>68400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>27600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>600</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
@@ -900,8 +909,11 @@
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -921,50 +933,51 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E12" s="3">
         <v>37500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>43700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>48600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>47300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>52700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>70200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>104700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>134200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>82000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>87100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>65500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>126600</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
@@ -974,8 +987,11 @@
       <c r="S12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1027,47 +1043,50 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>51500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>-1400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-2200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1080,52 +1099,55 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E15" s="3">
         <v>19100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>17800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>19100</v>
       </c>
       <c r="G15" s="3">
         <v>19100</v>
       </c>
       <c r="H15" s="3">
+        <v>19100</v>
+      </c>
+      <c r="I15" s="3">
         <v>13700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>19600</v>
-      </c>
-      <c r="J15" s="3">
-        <v>13700</v>
       </c>
       <c r="K15" s="3">
         <v>13700</v>
       </c>
       <c r="L15" s="3">
+        <v>13700</v>
+      </c>
+      <c r="M15" s="3">
         <v>3200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2200</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1133,8 +1155,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1151,114 +1176,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>229300</v>
+      </c>
+      <c r="E17" s="3">
         <v>231000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>234400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>195800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>460100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>414700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>429400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>406400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>589100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>351400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>293600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>180900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>186800</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-93500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-108900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-103000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-188600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-160000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-204400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-233300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-228100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-163500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-182600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-161800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-184400</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1278,103 +1310,107 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-28200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-32800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>56200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>224100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>50500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>21100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>15600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-16300</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-46200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-58400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-140100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-393600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-196800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-186300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-240700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-209500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-162500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-187000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-156600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-198400</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1384,52 +1420,55 @@
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E22" s="3">
         <v>7400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>-600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>34300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>37700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>5500</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1437,105 +1476,111 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-86500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-63800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-115800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-182200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-439900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-205500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-201800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-258100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-224000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-172200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-193300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-159700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-206200</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3">
         <v>4500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1543,8 +1588,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1596,114 +1644,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-85800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-65400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-130200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-182800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-440800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-206300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-202000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-258200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-223700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-173600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-193400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-159600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-206300</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3">
         <v>4500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-85800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-65400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-130200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-182800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-439800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-205800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-201500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-260800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-233200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-176500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-182500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-164900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-206300</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3">
         <v>4500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1755,8 +1812,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1808,8 +1868,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1861,8 +1924,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1914,114 +1980,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E32" s="3">
         <v>28200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>32800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-56200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-224100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-50500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-21100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-15600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>16300</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>-5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-85800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-65400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-130200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-182800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-439800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-205800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-201500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-257900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-223100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-171700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-189500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-157700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-206300</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3">
         <v>4500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2073,119 +2148,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-85800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-65400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-130200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-182800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-439800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-205800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-201500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-257900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-223100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-171700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-189500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-157700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-206300</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3">
         <v>4500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2205,8 +2289,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2226,105 +2311,109 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E41" s="3">
         <v>65300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>67800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>122600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>103100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>191300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>268800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>232900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>418900</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
         <v>548300</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R41" s="3">
         <v>100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>2900</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>3400</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>5000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>4000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>2600</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2332,52 +2421,55 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>184200</v>
+      </c>
+      <c r="E43" s="3">
         <v>137500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>210400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>182300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>270700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>151100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>92500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>146100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>106500</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>28500</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2385,52 +2477,55 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>204700</v>
+      </c>
+      <c r="E44" s="3">
         <v>116800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>208500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>143400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>221800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>320800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>385200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>368500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>286600</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>134500</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2438,211 +2533,223 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>70200</v>
+      </c>
+      <c r="E45" s="3">
         <v>223600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>143000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>159000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>64600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>165600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>153900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>309600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>59800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>13400</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>911100</v>
+      </c>
+      <c r="E46" s="3">
         <v>903900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1053600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1013700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1042900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1294000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1279200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1332700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>883700</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N46" s="3">
         <v>907400</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R46" s="3">
         <v>400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E47" s="3">
         <v>15100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>14300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7800</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>11800</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R47" s="3">
         <v>286900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>286600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>286500</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>345700</v>
+      </c>
+      <c r="E48" s="3">
         <v>361000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>369900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>451900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>460500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>496800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>504200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>520800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>527700</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" s="3">
         <v>457200</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -2650,8 +2757,11 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2674,28 +2784,28 @@
         <v>116500</v>
       </c>
       <c r="J49" s="3">
-        <v>116400</v>
+        <v>116500</v>
       </c>
       <c r="K49" s="3">
         <v>116400</v>
       </c>
       <c r="L49" s="3">
-        <v>0</v>
+        <v>116400</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>116400</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -2703,8 +2813,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2756,8 +2869,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2809,61 +2925,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E52" s="3">
         <v>160400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>395200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>394100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>386500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>397100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>375500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>368600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>49100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3">
         <v>102400</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2915,61 +3037,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1952700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1858300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2252100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2266900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2285700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2587200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2506300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2543500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1584700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>1595200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R54" s="3">
         <v>287400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>287500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>287600</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2989,8 +3117,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3010,52 +3139,53 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>722600</v>
+      </c>
+      <c r="E57" s="3">
         <v>501100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>670600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>364500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>681800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>549000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>695100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>444600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>605500</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>167600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -3063,52 +3193,55 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1403100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1258600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1160300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1120100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>931600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>934700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>644700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>479000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>643300</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>766400</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3116,150 +3249,159 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>93400</v>
+      </c>
+      <c r="E59" s="3">
         <v>25300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>161200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>155000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>579600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>48400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>196100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>62300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>235500</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>165200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2398100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2255200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2235500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2246400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2467400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2130000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1840500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1702500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1757300</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>1456500</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R60" s="3">
         <v>1200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>438200</v>
+      </c>
+      <c r="E61" s="3">
         <v>439600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>334000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>261000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>256300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>269400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>245800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>257100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>261300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>242300</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3275,61 +3417,67 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>126700</v>
+      </c>
+      <c r="E62" s="3">
         <v>120000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>482500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>498400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>119600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>256300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>290600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>287300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>116900</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>39200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3">
         <v>11600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>16200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3381,8 +3529,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3434,8 +3585,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3487,61 +3641,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3283000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3120800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3354700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3308100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3145900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2964800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2680300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2523700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2411900</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>2005000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R66" s="3">
         <v>12800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3561,8 +3721,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3614,8 +3775,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3667,8 +3831,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3694,20 +3861,20 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>383500</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>368700</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>368400</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3720,8 +3887,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3773,61 +3943,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3157900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3072200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3006700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2876500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2693700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2253900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2048100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1846600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1588800</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-1193900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>-12300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-16400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-21100</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3879,8 +4055,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3932,8 +4111,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3985,61 +4167,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1322500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1254800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1094800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1033500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-852900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-371000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-167700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1205300</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N76" s="3">
         <v>-772200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-452400</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R76" s="3">
         <v>274600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>270100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>265400</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4091,119 +4279,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q80" s="2">
+      <c r="Q80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-85800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-65400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-130200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-182800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-439800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-205800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-201500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-257900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-223100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-171700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-189500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-157700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-206300</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3">
         <v>4500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4223,8 +4420,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4249,11 +4447,11 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
         <v>7300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>1100</v>
       </c>
       <c r="M83" s="3">
         <v>1100</v>
@@ -4262,7 +4460,7 @@
         <v>1100</v>
       </c>
       <c r="O83" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -4276,8 +4474,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4329,8 +4530,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4382,8 +4586,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4435,8 +4642,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4488,8 +4698,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4541,8 +4754,11 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4585,17 +4801,20 @@
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4615,8 +4834,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4653,8 +4873,8 @@
       <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -4668,8 +4888,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4721,8 +4944,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4774,8 +5000,11 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4818,8 +5047,8 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -4827,8 +5056,11 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4848,8 +5080,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4886,8 +5119,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -4901,8 +5134,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4954,8 +5190,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5007,8 +5246,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5060,8 +5302,11 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5104,8 +5349,8 @@
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -5113,8 +5358,11 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5139,26 +5387,26 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3">
         <v>16400</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-13500</v>
       </c>
       <c r="M101" s="3">
         <v>-13500</v>
       </c>
       <c r="N101" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="O101" s="3">
         <v>4200</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -5166,8 +5414,11 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5204,19 +5455,22 @@
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3">
         <v>-300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
     </row>
